--- a/school_2/1) walls/Перегородки/перегородки-Ш2.xlsx
+++ b/school_2/1) walls/Перегородки/перегородки-Ш2.xlsx
@@ -1311,8 +1311,8 @@
         <v>5</v>
       </c>
       <c r="E2" s="8">
-        <f>338.36+184.48</f>
-        <v>522.84</v>
+        <f>184.48</f>
+        <v>184.48</v>
       </c>
     </row>
   </sheetData>
